--- a/data/trans_orig/IP18E-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP18E-Edad-trans_orig.xlsx
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>682</t>
+          <t>705</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6266</t>
+          <t>6270</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2652</t>
+          <t>2633</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11061</t>
+          <t>10177</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4292</t>
+          <t>4738</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>13259</t>
+          <t>13242</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>616</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5570</t>
+          <t>5454</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2673</t>
+          <t>2730</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10532</t>
+          <t>10678</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4623</t>
+          <t>4675</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>14138</t>
+          <t>13931</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,71%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>91282</t>
+          <t>91477</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>98298</t>
+          <t>98327</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>90,88%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>89324</t>
+          <t>89300</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>100316</t>
+          <t>100002</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>83,45%</t>
+          <t>83,43%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>183478</t>
+          <t>183962</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>196654</t>
+          <t>196465</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>88,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,6%</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3852</t>
+          <t>3808</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>3432</t>
+          <t>3438</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4005</t>
+          <t>3945</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12728</t>
+          <t>12707</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2745</t>
+          <t>2715</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11021</t>
+          <t>10497</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8594</t>
+          <t>8469</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19729</t>
+          <t>19864</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,35%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4699</t>
+          <t>4703</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13566</t>
+          <t>13866</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4544</t>
+          <t>3936</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13156</t>
+          <t>12996</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>10387</t>
+          <t>10422</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>22821</t>
+          <t>23774</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,2%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>204390</t>
+          <t>205108</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>216565</t>
+          <t>217256</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>89,84%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>208515</t>
+          <t>208387</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>219747</t>
+          <t>220839</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>90,78%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>417824</t>
+          <t>417551</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>434555</t>
+          <t>434318</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>91,36%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>95,03%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>936</t>
+          <t>1078</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6150</t>
+          <t>6793</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2253</t>
+          <t>2245</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>10423</t>
+          <t>9753</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>4437</t>
+          <t>4339</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>13789</t>
+          <t>13937</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,44%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1426</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8673</t>
+          <t>8215</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3764</t>
+          <t>4063</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2366</t>
+          <t>2300</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9847</t>
+          <t>9641</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,46%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>91851</t>
+          <t>91840</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>99836</t>
+          <t>99872</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,77%</t>
+          <t>88,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>101151</t>
+          <t>101075</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>109645</t>
+          <t>109561</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>89,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>196438</t>
+          <t>196700</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>208276</t>
+          <t>208321</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,81%</t>
+          <t>90,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,3%</t>
         </is>
       </c>
     </row>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3760</t>
+          <t>3433</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3418</t>
+          <t>3528</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,1%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3046</t>
+          <t>3089</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>12084</t>
+          <t>11995</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1317</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>7888</t>
+          <t>7856</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5694</t>
+          <t>5800</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>16699</t>
+          <t>17389</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,41%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>733</t>
+          <t>678</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7410</t>
+          <t>6940</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3513</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>12815</t>
+          <t>12558</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>5400</t>
+          <t>5691</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>15421</t>
+          <t>15914</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,95%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>141624</t>
+          <t>141260</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>151529</t>
+          <t>151569</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>89,77%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>147373</t>
+          <t>147326</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>158037</t>
+          <t>157767</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>89,91%</t>
+          <t>89,89%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>292642</t>
+          <t>291990</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>307499</t>
+          <t>306999</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>90,89%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,56%</t>
         </is>
       </c>
     </row>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3883</t>
+          <t>3417</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3029,7 +3029,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3158</t>
+          <t>3690</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3064,7 +3064,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>4710</t>
+          <t>4792</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,4%</t>
         </is>
       </c>
     </row>
@@ -3122,12 +3122,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>13763</t>
+          <t>13417</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>27666</t>
+          <t>27786</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,12 +3137,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>13579</t>
+          <t>13774</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>28706</t>
+          <t>28369</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,12 +3172,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>31246</t>
+          <t>30917</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>50940</t>
+          <t>51125</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,12 +3207,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,25%</t>
         </is>
       </c>
     </row>
@@ -3235,12 +3235,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>11426</t>
+          <t>12233</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>25052</t>
+          <t>25978</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3250,12 +3250,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>15274</t>
+          <t>14786</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>30270</t>
+          <t>29742</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,12 +3285,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>30826</t>
+          <t>30864</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>49963</t>
+          <t>50911</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,23%</t>
         </is>
       </c>
     </row>
@@ -3348,12 +3348,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>541227</t>
+          <t>541509</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>559988</t>
+          <t>559492</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3363,12 +3363,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>559770</t>
+          <t>559408</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>579694</t>
+          <t>579792</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>91,27%</t>
+          <t>91,21%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1106523</t>
+          <t>1106063</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1134395</t>
+          <t>1134911</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>92,0%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,39%</t>
         </is>
       </c>
     </row>
@@ -3923,12 +3923,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1380</t>
+          <t>1834</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9166</t>
+          <t>9129</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3938,12 +3938,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3958,12 +3958,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>667</t>
+          <t>678</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6955</t>
+          <t>6942</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3993,12 +3993,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3610</t>
+          <t>3601</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>12470</t>
+          <t>12754</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4013,7 +4013,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,5%</t>
         </is>
       </c>
     </row>
@@ -4036,12 +4036,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>2542</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10176</t>
+          <t>10495</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4051,12 +4051,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1236</t>
+          <t>1221</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8196</t>
+          <t>8100</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5359</t>
+          <t>5105</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>15295</t>
+          <t>15194</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,36%</t>
         </is>
       </c>
     </row>
@@ -4149,12 +4149,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>125614</t>
+          <t>124627</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>136061</t>
+          <t>135898</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4164,12 +4164,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>88,77%</t>
+          <t>88,08%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>130527</t>
+          <t>129898</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>138806</t>
+          <t>138729</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>91,56%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>259852</t>
+          <t>259643</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>272292</t>
+          <t>272747</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,25%</t>
         </is>
       </c>
     </row>
@@ -4492,12 +4492,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>707</t>
+          <t>706</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7858</t>
+          <t>7091</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4512,7 +4512,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1327</t>
+          <t>1331</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7349</t>
+          <t>7467</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4547,7 +4547,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4567,7 +4567,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11080</t>
+          <t>11696</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,45%</t>
         </is>
       </c>
     </row>
@@ -4605,12 +4605,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2645</t>
+          <t>2627</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11422</t>
+          <t>10814</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4620,12 +4620,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5420</t>
+          <t>4853</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15242</t>
+          <t>15536</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>9488</t>
+          <t>9662</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>21951</t>
+          <t>22061</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4690,12 +4690,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,62%</t>
         </is>
       </c>
     </row>
@@ -4718,12 +4718,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>206745</t>
+          <t>207125</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>217178</t>
+          <t>216916</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4733,12 +4733,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>236900</t>
+          <t>237092</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>248077</t>
+          <t>248351</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4768,12 +4768,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>448192</t>
+          <t>448418</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>462959</t>
+          <t>463446</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4803,12 +4803,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>97,05%</t>
         </is>
       </c>
     </row>
@@ -4953,7 +4953,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4569</t>
+          <t>4911</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5023,7 +5023,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4625</t>
+          <t>4646</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5038,7 +5038,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,55%</t>
         </is>
       </c>
     </row>
@@ -5061,12 +5061,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>704</t>
+          <t>740</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6426</t>
+          <t>7091</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5076,47 +5076,47 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
+          <t>0,49%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>4,69%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>2946</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>695</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>7349</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>1,97%</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
           <t>0,47%</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>4,25%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>2946</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>704</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>7299</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>1,97%</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2756</t>
+          <t>2717</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>11531</t>
+          <t>11680</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5146,12 +5146,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,89%</t>
         </is>
       </c>
     </row>
@@ -5174,12 +5174,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1543</t>
+          <t>2079</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9429</t>
+          <t>9211</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5189,12 +5189,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3664</t>
+          <t>3563</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13025</t>
+          <t>12709</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5224,12 +5224,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5244,12 +5244,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7027</t>
+          <t>6872</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>18236</t>
+          <t>18781</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,25%</t>
         </is>
       </c>
     </row>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>136886</t>
+          <t>137085</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>146905</t>
+          <t>146837</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5302,12 +5302,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>90,69%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5322,12 +5322,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>132210</t>
+          <t>133189</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>143364</t>
+          <t>143909</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5337,12 +5337,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,55%</t>
+          <t>89,21%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5357,12 +5357,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>274333</t>
+          <t>274141</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>288662</t>
+          <t>288620</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5372,12 +5372,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>91,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,06%</t>
         </is>
       </c>
     </row>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3468</t>
+          <t>3445</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5537,7 +5537,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3274</t>
+          <t>3295</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5607,7 +5607,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,04%</t>
         </is>
       </c>
     </row>
@@ -5630,12 +5630,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1275</t>
+          <t>1282</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7524</t>
+          <t>6814</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5645,12 +5645,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5665,12 +5665,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1244</t>
+          <t>1481</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>7855</t>
+          <t>7928</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5680,12 +5680,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5700,12 +5700,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3502</t>
+          <t>3603</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>11623</t>
+          <t>11601</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5715,7 +5715,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -5743,12 +5743,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1864</t>
+          <t>1771</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>8777</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5758,12 +5758,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5778,12 +5778,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2583</t>
+          <t>2592</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>10147</t>
+          <t>10271</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5798,7 +5798,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5813,12 +5813,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>5990</t>
+          <t>6138</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>15499</t>
+          <t>16291</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5828,12 +5828,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,15%</t>
         </is>
       </c>
     </row>
@@ -5856,12 +5856,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>138143</t>
+          <t>138571</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>147044</t>
+          <t>147082</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5871,12 +5871,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5891,12 +5891,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>150364</t>
+          <t>150487</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>160153</t>
+          <t>159875</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5906,12 +5906,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>91,31%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5926,12 +5926,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>292401</t>
+          <t>290942</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>304817</t>
+          <t>304409</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,2%</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>6677</t>
+          <t>5995</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6106,7 +6106,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6058</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6176,7 +6176,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,38%</t>
         </is>
       </c>
     </row>
@@ -6199,12 +6199,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>8427</t>
+          <t>7860</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>21004</t>
+          <t>20212</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6214,12 +6214,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6234,12 +6234,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>7596</t>
+          <t>7939</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>19749</t>
+          <t>19477</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6249,12 +6249,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6269,12 +6269,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>18469</t>
+          <t>18375</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>34866</t>
+          <t>34618</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6284,12 +6284,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,51%</t>
         </is>
       </c>
     </row>
@@ -6312,12 +6312,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>13831</t>
+          <t>14014</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>29262</t>
+          <t>29350</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6327,12 +6327,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6347,12 +6347,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>18509</t>
+          <t>17866</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>35339</t>
+          <t>35080</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6362,12 +6362,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6382,12 +6382,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>35026</t>
+          <t>34825</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>58590</t>
+          <t>57344</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6397,12 +6397,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,16%</t>
         </is>
       </c>
     </row>
@@ -6425,12 +6425,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>620381</t>
+          <t>619523</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>639591</t>
+          <t>640023</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6440,12 +6440,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6460,12 +6460,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>662339</t>
+          <t>661538</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>682374</t>
+          <t>682051</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -6495,12 +6495,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1290435</t>
+          <t>1291657</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1318748</t>
+          <t>1317988</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,66%</t>
         </is>
       </c>
     </row>
@@ -7000,12 +7000,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>821</t>
+          <t>759</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6765</t>
+          <t>6526</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7015,12 +7015,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7035,12 +7035,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>697</t>
+          <t>710</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6638</t>
+          <t>6309</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7050,12 +7050,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7070,12 +7070,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2087</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>9331</t>
+          <t>9622</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7085,12 +7085,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,96%</t>
         </is>
       </c>
     </row>
@@ -7113,12 +7113,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>2885</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10934</t>
+          <t>10619</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7128,12 +7128,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7148,12 +7148,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3197</t>
+          <t>3100</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11163</t>
+          <t>10920</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7163,12 +7163,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7183,12 +7183,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>7372</t>
+          <t>7655</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>18638</t>
+          <t>18197</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7198,12 +7198,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,49%</t>
         </is>
       </c>
     </row>
@@ -7226,12 +7226,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>113438</t>
+          <t>112766</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>122068</t>
+          <t>122169</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7241,12 +7241,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>89,39%</t>
+          <t>88,86%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>101842</t>
+          <t>101858</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>111012</t>
+          <t>110967</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7276,12 +7276,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>87,67%</t>
+          <t>87,69%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7296,12 +7296,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>218530</t>
+          <t>218265</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>231143</t>
+          <t>231054</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7311,12 +7311,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>89,91%</t>
+          <t>89,8%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,06%</t>
         </is>
       </c>
     </row>
@@ -7569,12 +7569,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>621</t>
+          <t>620</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6431</t>
+          <t>5921</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7589,7 +7589,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>893</t>
+          <t>1173</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7107</t>
+          <t>7284</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7619,12 +7619,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2638</t>
+          <t>3073</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10135</t>
+          <t>10795</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,51%</t>
         </is>
       </c>
     </row>
@@ -7682,12 +7682,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4357</t>
+          <t>4214</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13042</t>
+          <t>13615</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7697,12 +7697,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7717,12 +7717,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5291</t>
+          <t>4974</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14038</t>
+          <t>14620</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>11206</t>
+          <t>11212</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>24655</t>
+          <t>23607</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,49%</t>
         </is>
       </c>
     </row>
@@ -7795,12 +7795,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>178848</t>
+          <t>178578</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>188718</t>
+          <t>188502</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7810,12 +7810,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7830,12 +7830,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>216785</t>
+          <t>216811</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>227428</t>
+          <t>227555</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>398927</t>
+          <t>399001</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>413755</t>
+          <t>413955</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,31%</t>
         </is>
       </c>
     </row>
@@ -8138,12 +8138,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1886</t>
+          <t>1924</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9004</t>
+          <t>8955</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8153,12 +8153,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8178,7 +8178,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4490</t>
+          <t>5037</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8193,7 +8193,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2659</t>
+          <t>2622</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>10700</t>
+          <t>10241</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -8251,12 +8251,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3897</t>
+          <t>3877</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12283</t>
+          <t>12423</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8266,12 +8266,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8286,12 +8286,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3828</t>
+          <t>3798</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13254</t>
+          <t>12916</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8321,12 +8321,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9522</t>
+          <t>9059</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>22068</t>
+          <t>21613</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,34%</t>
         </is>
       </c>
     </row>
@@ -8364,12 +8364,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>153342</t>
+          <t>153634</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>164292</t>
+          <t>163858</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8379,12 +8379,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,52%</t>
+          <t>89,69%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8399,12 +8399,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>154612</t>
+          <t>155285</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>164334</t>
+          <t>164679</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8414,12 +8414,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8434,12 +8434,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>312392</t>
+          <t>312107</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>326600</t>
+          <t>326304</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,79%</t>
         </is>
       </c>
     </row>
@@ -8712,7 +8712,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3148</t>
+          <t>3694</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8727,7 +8727,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8742,12 +8742,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>722</t>
+          <t>729</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6238</t>
+          <t>6131</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8762,7 +8762,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8777,12 +8777,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>758</t>
+          <t>762</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6931</t>
+          <t>6794</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8797,7 +8797,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -8820,12 +8820,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3639</t>
+          <t>3934</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>12348</t>
+          <t>12917</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8835,12 +8835,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -8855,12 +8855,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3625</t>
+          <t>3556</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>13396</t>
+          <t>12295</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8870,12 +8870,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -8890,12 +8890,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>9345</t>
+          <t>9101</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>22015</t>
+          <t>21818</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8905,12 +8905,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,22%</t>
         </is>
       </c>
     </row>
@@ -8933,12 +8933,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>140560</t>
+          <t>139679</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>149698</t>
+          <t>149308</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8948,12 +8948,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>90,81%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>132158</t>
+          <t>133232</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>143462</t>
+          <t>143484</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8983,12 +8983,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>88,96%</t>
+          <t>89,68%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>276754</t>
+          <t>276664</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>290509</t>
+          <t>290604</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9018,12 +9018,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,11%</t>
         </is>
       </c>
     </row>
@@ -9276,12 +9276,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6078</t>
+          <t>5902</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>15972</t>
+          <t>16344</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9311,12 +9311,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5285</t>
+          <t>5304</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>14904</t>
+          <t>14876</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9331,7 +9331,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9346,12 +9346,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>13072</t>
+          <t>13429</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>27096</t>
+          <t>27762</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9361,12 +9361,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -9389,12 +9389,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>21102</t>
+          <t>20795</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>39048</t>
+          <t>38130</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9404,12 +9404,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>21999</t>
+          <t>22614</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>39602</t>
+          <t>38859</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>47739</t>
+          <t>46877</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>71207</t>
+          <t>71711</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9474,12 +9474,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,45%</t>
         </is>
       </c>
     </row>
@@ -9502,12 +9502,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>597946</t>
+          <t>597539</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>616934</t>
+          <t>616918</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9517,7 +9517,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>619551</t>
+          <t>619529</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>638985</t>
+          <t>638715</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9557,7 +9557,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1223471</t>
+          <t>1222887</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1251004</t>
+          <t>1251511</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -9587,12 +9587,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>95,11%</t>
         </is>
       </c>
     </row>
@@ -10077,12 +10077,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>555</t>
+          <t>577</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4739</t>
+          <t>4665</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10092,12 +10092,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10152,7 +10152,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5473</t>
+          <t>5212</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10167,7 +10167,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,0%</t>
         </is>
       </c>
     </row>
@@ -10195,7 +10195,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3348</t>
+          <t>3212</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10210,7 +10210,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -10230,7 +10230,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2132</t>
+          <t>2424</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10245,7 +10245,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>426</t>
+          <t>422</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>3988</t>
+          <t>3901</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10275,12 +10275,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,23%</t>
         </is>
       </c>
     </row>
@@ -10303,12 +10303,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10578</t>
+          <t>10658</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15234</t>
+          <t>15128</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>64,92%</t>
+          <t>65,41%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10338,7 +10338,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16315</t>
+          <t>16023</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -10353,7 +10353,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>88,44%</t>
+          <t>86,86%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>28164</t>
+          <t>27705</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>33361</t>
+          <t>33310</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>81,07%</t>
+          <t>79,75%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>95,88%</t>
         </is>
       </c>
     </row>
@@ -10646,12 +10646,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>541</t>
+          <t>583</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>5046</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10661,12 +10661,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10681,12 +10681,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>545</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5868</t>
+          <t>6259</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10696,12 +10696,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10716,12 +10716,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1767</t>
+          <t>2029</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8892</t>
+          <t>8863</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,31%</t>
         </is>
       </c>
     </row>
@@ -10764,7 +10764,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4158</t>
+          <t>4258</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10779,7 +10779,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>449</t>
+          <t>435</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5801</t>
+          <t>5478</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10809,12 +10809,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1225</t>
+          <t>1237</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>7894</t>
+          <t>7978</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,88%</t>
         </is>
       </c>
     </row>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>21442</t>
+          <t>21200</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>26858</t>
+          <t>26793</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10887,12 +10887,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>76,04%</t>
+          <t>75,18%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>25712</t>
+          <t>25262</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>31990</t>
+          <t>32130</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10922,12 +10922,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>76,23%</t>
+          <t>74,9%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>48563</t>
+          <t>48574</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>57900</t>
+          <t>57673</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10957,12 +10957,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>78,42%</t>
+          <t>78,44%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>93,13%</t>
         </is>
       </c>
     </row>
@@ -11107,7 +11107,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2219</t>
+          <t>2280</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11122,7 +11122,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11177,7 +11177,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1734</t>
+          <t>2055</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11192,7 +11192,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -11215,12 +11215,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1622</t>
+          <t>1344</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>13286</t>
+          <t>12529</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11230,12 +11230,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>42,45%</t>
+          <t>40,03%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1431</t>
+          <t>1388</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>15998</t>
+          <t>15889</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11300,12 +11300,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,31%</t>
         </is>
       </c>
     </row>
@@ -11333,7 +11333,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4741</t>
+          <t>4103</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11348,7 +11348,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11368,7 +11368,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3101</t>
+          <t>2697</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11383,7 +11383,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11398,12 +11398,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>507</t>
+          <t>505</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5325</t>
+          <t>5417</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11418,7 +11418,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,95%</t>
         </is>
       </c>
     </row>
@@ -11441,12 +11441,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16828</t>
+          <t>17585</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>28170</t>
+          <t>28505</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11456,12 +11456,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>53,77%</t>
+          <t>56,19%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>91,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11476,7 +11476,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>33770</t>
+          <t>34174</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -11491,7 +11491,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -11511,12 +11511,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>50007</t>
+          <t>50773</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>64779</t>
+          <t>64733</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11526,12 +11526,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>73,36%</t>
+          <t>74,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>94,96%</t>
         </is>
       </c>
     </row>
@@ -11784,12 +11784,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>572</t>
+          <t>549</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5490</t>
+          <t>4751</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11799,12 +11799,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11824,7 +11824,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>5042</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11839,7 +11839,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1143</t>
+          <t>1229</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>7005</t>
+          <t>7014</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11869,12 +11869,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,46%</t>
         </is>
       </c>
     </row>
@@ -11902,7 +11902,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3053</t>
+          <t>3258</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11917,7 +11917,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11937,7 +11937,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>5456</t>
+          <t>5383</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11952,7 +11952,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>579</t>
+          <t>578</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>5351</t>
+          <t>5900</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11987,7 +11987,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,8%</t>
         </is>
       </c>
     </row>
@@ -12010,12 +12010,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>18463</t>
+          <t>18745</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>23830</t>
+          <t>23902</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12025,12 +12025,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>75,28%</t>
+          <t>76,43%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12045,12 +12045,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>35237</t>
+          <t>35787</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>41679</t>
+          <t>41701</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12060,12 +12060,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>82,82%</t>
+          <t>84,11%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12080,12 +12080,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>57467</t>
+          <t>57028</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>64676</t>
+          <t>64455</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12095,12 +12095,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>85,68%</t>
+          <t>85,03%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,1%</t>
         </is>
       </c>
     </row>
@@ -12245,7 +12245,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2096</t>
+          <t>1923</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -12260,7 +12260,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -12315,7 +12315,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>2099</t>
+          <t>1967</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12330,7 +12330,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,85%</t>
         </is>
       </c>
     </row>
@@ -12353,12 +12353,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6411</t>
+          <t>6098</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>21948</t>
+          <t>21697</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12368,12 +12368,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12388,12 +12388,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1212</t>
+          <t>1226</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>8400</t>
+          <t>8494</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12403,12 +12403,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>8946</t>
+          <t>9370</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>25843</t>
+          <t>26964</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12438,12 +12438,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,63%</t>
         </is>
       </c>
     </row>
@@ -12466,12 +12466,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1858</t>
+          <t>1920</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>9000</t>
+          <t>8045</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12481,12 +12481,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12501,12 +12501,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>2230</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>9215</t>
+          <t>9752</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12516,12 +12516,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12536,12 +12536,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4727</t>
+          <t>4786</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>14687</t>
+          <t>14420</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12551,12 +12551,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,22%</t>
         </is>
       </c>
     </row>
@@ -12579,12 +12579,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>74582</t>
+          <t>73912</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>89702</t>
+          <t>89845</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12594,12 +12594,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>74,35%</t>
+          <t>73,68%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -12614,12 +12614,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>117908</t>
+          <t>117893</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>127257</t>
+          <t>127020</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12629,12 +12629,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,59%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -12649,12 +12649,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>195974</t>
+          <t>196061</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>215015</t>
+          <t>215028</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -12664,7 +12664,7 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>84,51%</t>
+          <t>84,54%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
